--- a/ZonasEscolares/excels/LIMA-LIMA-SANTIAGO_DE_SURCO.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-SANTIAGO_DE_SURCO.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SANTIAGO_DE_SURCO</t>
+          <t>SANTIAGO DE SURCO</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SANTIAGO_DE_SURCO</t>
+          <t>SANTIAGO DE SURCO</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SANTIAGO_DE_SURCO</t>
+          <t>SANTIAGO DE SURCO</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SANTIAGO_DE_SURCO</t>
+          <t>SANTIAGO DE SURCO</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -716,7 +716,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SANTIAGO_DE_SURCO</t>
+          <t>SANTIAGO DE SURCO</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -768,7 +768,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SANTIAGO_DE_SURCO</t>
+          <t>SANTIAGO DE SURCO</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SANTIAGO_DE_SURCO</t>
+          <t>SANTIAGO DE SURCO</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SANTIAGO_DE_SURCO</t>
+          <t>SANTIAGO DE SURCO</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>SANTIAGO_DE_SURCO</t>
+          <t>SANTIAGO DE SURCO</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SANTIAGO_DE_SURCO</t>
+          <t>SANTIAGO DE SURCO</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>SANTIAGO_DE_SURCO</t>
+          <t>SANTIAGO DE SURCO</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SANTIAGO_DE_SURCO</t>
+          <t>SANTIAGO DE SURCO</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SANTIAGO_DE_SURCO</t>
+          <t>SANTIAGO DE SURCO</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SANTIAGO_DE_SURCO</t>
+          <t>SANTIAGO DE SURCO</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>SANTIAGO_DE_SURCO</t>
+          <t>SANTIAGO DE SURCO</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>SANTIAGO_DE_SURCO</t>
+          <t>SANTIAGO DE SURCO</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SANTIAGO_DE_SURCO</t>
+          <t>SANTIAGO DE SURCO</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SANTIAGO_DE_SURCO</t>
+          <t>SANTIAGO DE SURCO</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SANTIAGO_DE_SURCO</t>
+          <t>SANTIAGO DE SURCO</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>SANTIAGO_DE_SURCO</t>
+          <t>SANTIAGO DE SURCO</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>SANTIAGO_DE_SURCO</t>
+          <t>SANTIAGO DE SURCO</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>SANTIAGO_DE_SURCO</t>
+          <t>SANTIAGO DE SURCO</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>SANTIAGO_DE_SURCO</t>
+          <t>SANTIAGO DE SURCO</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>SANTIAGO_DE_SURCO</t>
+          <t>SANTIAGO DE SURCO</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>SANTIAGO_DE_SURCO</t>
+          <t>SANTIAGO DE SURCO</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>SANTIAGO_DE_SURCO</t>
+          <t>SANTIAGO DE SURCO</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>SANTIAGO_DE_SURCO</t>
+          <t>SANTIAGO DE SURCO</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>SANTIAGO_DE_SURCO</t>
+          <t>SANTIAGO DE SURCO</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>SANTIAGO_DE_SURCO</t>
+          <t>SANTIAGO DE SURCO</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>SANTIAGO_DE_SURCO</t>
+          <t>SANTIAGO DE SURCO</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>SANTIAGO_DE_SURCO</t>
+          <t>SANTIAGO DE SURCO</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>SANTIAGO_DE_SURCO</t>
+          <t>SANTIAGO DE SURCO</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>SANTIAGO_DE_SURCO</t>
+          <t>SANTIAGO DE SURCO</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>SANTIAGO_DE_SURCO</t>
+          <t>SANTIAGO DE SURCO</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2276,7 +2276,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>SANTIAGO_DE_SURCO</t>
+          <t>SANTIAGO DE SURCO</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>SANTIAGO_DE_SURCO</t>
+          <t>SANTIAGO DE SURCO</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>SANTIAGO_DE_SURCO</t>
+          <t>SANTIAGO DE SURCO</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>SANTIAGO_DE_SURCO</t>
+          <t>SANTIAGO DE SURCO</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>SANTIAGO_DE_SURCO</t>
+          <t>SANTIAGO DE SURCO</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>SANTIAGO_DE_SURCO</t>
+          <t>SANTIAGO DE SURCO</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>SANTIAGO_DE_SURCO</t>
+          <t>SANTIAGO DE SURCO</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>SANTIAGO_DE_SURCO</t>
+          <t>SANTIAGO DE SURCO</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>SANTIAGO_DE_SURCO</t>
+          <t>SANTIAGO DE SURCO</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>SANTIAGO_DE_SURCO</t>
+          <t>SANTIAGO DE SURCO</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>SANTIAGO_DE_SURCO</t>
+          <t>SANTIAGO DE SURCO</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>SANTIAGO_DE_SURCO</t>
+          <t>SANTIAGO DE SURCO</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>SANTIAGO_DE_SURCO</t>
+          <t>SANTIAGO DE SURCO</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>SANTIAGO_DE_SURCO</t>
+          <t>SANTIAGO DE SURCO</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>SANTIAGO_DE_SURCO</t>
+          <t>SANTIAGO DE SURCO</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>SANTIAGO_DE_SURCO</t>
+          <t>SANTIAGO DE SURCO</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>SANTIAGO_DE_SURCO</t>
+          <t>SANTIAGO DE SURCO</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>SANTIAGO_DE_SURCO</t>
+          <t>SANTIAGO DE SURCO</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3212,7 +3212,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>SANTIAGO_DE_SURCO</t>
+          <t>SANTIAGO DE SURCO</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>SANTIAGO_DE_SURCO</t>
+          <t>SANTIAGO DE SURCO</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>SANTIAGO_DE_SURCO</t>
+          <t>SANTIAGO DE SURCO</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/LIMA-LIMA-SANTIAGO_DE_SURCO.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-SANTIAGO_DE_SURCO.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>SANTA RITA DE CASIA</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-12.12902</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-77.00854</v>
-      </c>
-      <c r="I2" t="n">
-        <v>593</v>
-      </c>
-      <c r="J2" t="n">
-        <v>52</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-12.12902</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-77.00854</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>593</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>536 AMIGUITOS DE JESUS</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-12.13696</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-77.00099</v>
-      </c>
-      <c r="I3" t="n">
-        <v>231</v>
-      </c>
-      <c r="J3" t="n">
-        <v>11</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-12.13696</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-77.00099</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>555 INMACULADA CONCEPCION</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-12.15571</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-76.98864</v>
-      </c>
-      <c r="I4" t="n">
-        <v>299</v>
-      </c>
-      <c r="J4" t="n">
-        <v>14</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-12.15571</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-76.98864</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>557 WARMA KUYAY</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-12.14509</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-76.98359000000001</v>
-      </c>
-      <c r="I5" t="n">
-        <v>211</v>
-      </c>
-      <c r="J5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-12.14509</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-76.98359</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>6044 JORGE CHAVEZ</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-12.14332</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-77.00457</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1166</v>
-      </c>
-      <c r="J6" t="n">
-        <v>61</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-12.14332</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-77.00457</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1166</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>6047 JOSE MARIA ARGUEDAS</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-12.14896</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-76.98972000000001</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1144</v>
-      </c>
-      <c r="J7" t="n">
-        <v>59</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-12.14896</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-76.98972</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1144</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>6082 LOS PROCERES</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-12.15068</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-76.98486</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1787</v>
-      </c>
-      <c r="J8" t="n">
-        <v>92</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-12.15068</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-76.98486</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1787</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>6087 PABLO MARIA GUZMAN</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-12.09525</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-76.96393</v>
-      </c>
-      <c r="I9" t="n">
-        <v>575</v>
-      </c>
-      <c r="J9" t="n">
-        <v>34</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-12.09525</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-76.96393</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>575</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>7058 MARIA DE FATIMA</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-12.14506</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-77.00426</v>
-      </c>
-      <c r="I10" t="n">
-        <v>620</v>
-      </c>
-      <c r="J10" t="n">
-        <v>32</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-12.14506</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-77.00426</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>620</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>7068 ABRAHAM ROLDAN POMA</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-12.14689</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-77.0078</v>
-      </c>
-      <c r="I11" t="n">
-        <v>288</v>
-      </c>
-      <c r="J11" t="n">
-        <v>12</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-12.14689</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-77.0078</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>7068 ABRAHAM ROLDAN POMA</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-12.14561</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-77.0061</v>
-      </c>
-      <c r="I12" t="n">
-        <v>592</v>
-      </c>
-      <c r="J12" t="n">
-        <v>28</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-12.14561</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-77.0061</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>592</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>7086 LOS PRECURSORES</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-12.15677</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-76.9858</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1888</v>
-      </c>
-      <c r="J13" t="n">
-        <v>90</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-12.15677</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-76.9858</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1888</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>086 VIRGENCITA DEL CARMEN</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-12.14468</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-77.00405000000001</v>
-      </c>
-      <c r="I14" t="n">
-        <v>286</v>
-      </c>
-      <c r="J14" t="n">
-        <v>14</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-12.14468</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-77.00405</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>87 CORAZON DE MARIA</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-12.15392</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-76.98663999999999</v>
-      </c>
-      <c r="I15" t="n">
-        <v>436</v>
-      </c>
-      <c r="J15" t="n">
-        <v>18</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-12.15392</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-76.98664</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>436</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>VICTORIA BARCIA BONIFFATTI</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-12.12039</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-76.99339999999999</v>
-      </c>
-      <c r="I16" t="n">
-        <v>305</v>
-      </c>
-      <c r="J16" t="n">
-        <v>17</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-12.12039</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-76.9934</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>305</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>7087 SANTIAGO DE SURCO</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-12.143777</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-76.98336399999999</v>
-      </c>
-      <c r="I17" t="n">
-        <v>470</v>
-      </c>
-      <c r="J17" t="n">
-        <v>23</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-12.143777</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-76.983364</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>470</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>PNP CAP. ALCIDES VIGO HURTADO</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-12.12264</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-76.99421</v>
-      </c>
-      <c r="I18" t="n">
-        <v>629</v>
-      </c>
-      <c r="J18" t="n">
-        <v>41</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-12.12264</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-76.99421</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>629</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>ANDRE MALRAUX</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-12.12482</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-76.97922</v>
-      </c>
-      <c r="I19" t="n">
-        <v>372</v>
-      </c>
-      <c r="J19" t="n">
-        <v>39</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-12.12482</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-76.97922</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>CORAZON INMACULADO</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-12.14443</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-76.98693</v>
-      </c>
-      <c r="I20" t="n">
-        <v>96</v>
-      </c>
-      <c r="J20" t="n">
-        <v>13</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-12.14443</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-76.98693</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>CRISTO SALVADOR</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-12.12681</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-76.99563000000001</v>
-      </c>
-      <c r="I21" t="n">
-        <v>752</v>
-      </c>
-      <c r="J21" t="n">
-        <v>74</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-12.12681</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-76.99563</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>752</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>VILLA ALEGRE</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-12.16562</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-76.99159</v>
-      </c>
-      <c r="I22" t="n">
-        <v>227</v>
-      </c>
-      <c r="J22" t="n">
-        <v>18</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-12.16562</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-76.99159</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>FIGURITAS</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-12.12812</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-76.99596</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-12.12812</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-76.99596</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>GOTITAS DE CRISTAL</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-12.14778</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-77.00955</v>
-      </c>
-      <c r="I24" t="n">
-        <v>2</v>
-      </c>
-      <c r="J24" t="n">
-        <v>2</v>
-      </c>
-      <c r="K24" t="n">
-        <v>1</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-12.14778</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-77.00955</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>HORACIO PATIÑO CRUZATTI</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-12.13197</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-76.98582</v>
-      </c>
-      <c r="I25" t="n">
-        <v>622</v>
-      </c>
-      <c r="J25" t="n">
-        <v>46</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-12.13197</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-76.98582</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>622</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1769,20 +1997,30 @@
           <t>JUAN JACOBO ROUSSEAU</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-12.08386</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-76.97856</v>
-      </c>
-      <c r="I26" t="n">
-        <v>17</v>
-      </c>
-      <c r="J26" t="n">
-        <v>9</v>
-      </c>
-      <c r="K26" t="n">
-        <v>1</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-12.08386</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-76.97856</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1821,20 +2059,30 @@
           <t>COLEGIO DE LA INMACULADA (JESUITAS)</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-12.13024</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-76.97277</v>
-      </c>
-      <c r="I27" t="n">
-        <v>1515</v>
-      </c>
-      <c r="J27" t="n">
-        <v>151</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-12.13024</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-76.97277</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1515</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1873,20 +2121,30 @@
           <t>LA INMACULADA CONCEPCION</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-12.12794</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-76.99928</v>
-      </c>
-      <c r="I28" t="n">
-        <v>1494</v>
-      </c>
-      <c r="J28" t="n">
-        <v>85</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-12.12794</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-76.99928</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1494</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1925,20 +2183,30 @@
           <t>MAGISTER</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>-12.10407</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-76.97758</v>
-      </c>
-      <c r="I29" t="n">
-        <v>509</v>
-      </c>
-      <c r="J29" t="n">
-        <v>51</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-12.10407</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-76.97758</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1977,20 +2245,30 @@
           <t>MARISCAL CACERES</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>-12.14641</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-77.00793</v>
-      </c>
-      <c r="I30" t="n">
-        <v>206</v>
-      </c>
-      <c r="J30" t="n">
-        <v>17</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-12.14641</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-77.00793</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2029,20 +2307,30 @@
           <t>MARKHAM</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>-12.100516</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-76.976445</v>
-      </c>
-      <c r="I31" t="n">
-        <v>1248</v>
-      </c>
-      <c r="J31" t="n">
-        <v>103</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-12.100516</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-76.976445</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1248</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2081,20 +2369,30 @@
           <t>MATER CHRISTI</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>-12.12488</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-76.98245</v>
-      </c>
-      <c r="I32" t="n">
-        <v>456</v>
-      </c>
-      <c r="J32" t="n">
-        <v>43</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-12.12488</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-76.98245</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>456</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2133,20 +2431,30 @@
           <t>NUESTRA SEÑORA DE LA ASUNCION</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>-12.14435</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-76.98687</v>
-      </c>
-      <c r="I33" t="n">
-        <v>196</v>
-      </c>
-      <c r="J33" t="n">
-        <v>27</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-12.14435</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-76.98687</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2185,20 +2493,30 @@
           <t>NUEVO MUNDO</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>-12.12289</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-76.99456000000001</v>
-      </c>
-      <c r="I34" t="n">
-        <v>388</v>
-      </c>
-      <c r="J34" t="n">
-        <v>24</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-12.12289</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-76.99456</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2237,20 +2555,30 @@
           <t>PERUANO BRITANICO</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>-12.09255</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-76.97345</v>
-      </c>
-      <c r="I35" t="n">
-        <v>964</v>
-      </c>
-      <c r="J35" t="n">
-        <v>80</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-12.09255</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-76.97345</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>964</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2289,20 +2617,30 @@
           <t>PIO XII</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>-12.0979</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-76.96535</v>
-      </c>
-      <c r="I36" t="n">
-        <v>356</v>
-      </c>
-      <c r="J36" t="n">
-        <v>57</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-12.0979</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-76.96535</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>356</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2341,20 +2679,30 @@
           <t>RICHARD BACH</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>-12.15706</v>
-      </c>
-      <c r="H37" t="n">
-        <v>-76.98747</v>
-      </c>
-      <c r="I37" t="n">
-        <v>242</v>
-      </c>
-      <c r="J37" t="n">
-        <v>17</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-12.15706</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-76.98747</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2393,20 +2741,30 @@
           <t>SAN BENITO DE PALERMO</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>-12.15057</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-76.98875</v>
-      </c>
-      <c r="I38" t="n">
-        <v>364</v>
-      </c>
-      <c r="J38" t="n">
-        <v>24</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-12.15057</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-76.98875</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>364</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2445,20 +2803,30 @@
           <t>SAN JOSE DE MONTERRICO</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>-12.10991</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-76.96776</v>
-      </c>
-      <c r="I39" t="n">
-        <v>994</v>
-      </c>
-      <c r="J39" t="n">
-        <v>94</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-12.10991</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-76.96776</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>994</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2497,20 +2865,30 @@
           <t>SAN MARCOS DE MONTERRICO</t>
         </is>
       </c>
-      <c r="G40" t="n">
-        <v>-12.1277</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-76.97418</v>
-      </c>
-      <c r="I40" t="n">
-        <v>128</v>
-      </c>
-      <c r="J40" t="n">
-        <v>23</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-12.1277</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-76.97418</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2549,20 +2927,30 @@
           <t>SAN ROQUE</t>
         </is>
       </c>
-      <c r="G41" t="n">
-        <v>-12.14834</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-76.98878000000001</v>
-      </c>
-      <c r="I41" t="n">
-        <v>329</v>
-      </c>
-      <c r="J41" t="n">
-        <v>23</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-12.14834</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-76.98878</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>329</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2601,20 +2989,30 @@
           <t>SANTA ISABEL</t>
         </is>
       </c>
-      <c r="G42" t="n">
-        <v>-12.13333</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-76.99427</v>
-      </c>
-      <c r="I42" t="n">
-        <v>212</v>
-      </c>
-      <c r="J42" t="n">
-        <v>30</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-12.13333</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>-76.99427</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2653,20 +3051,30 @@
           <t>SANTA MARGARITA</t>
         </is>
       </c>
-      <c r="G43" t="n">
-        <v>-12.10094</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-76.973</v>
-      </c>
-      <c r="I43" t="n">
-        <v>718</v>
-      </c>
-      <c r="J43" t="n">
-        <v>62</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-12.10094</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>-76.973</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>718</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -2705,20 +3113,30 @@
           <t>SANTA MARIA MARIANISTA</t>
         </is>
       </c>
-      <c r="G44" t="n">
-        <v>-12.11377</v>
-      </c>
-      <c r="H44" t="n">
-        <v>-76.98768</v>
-      </c>
-      <c r="I44" t="n">
-        <v>1009</v>
-      </c>
-      <c r="J44" t="n">
-        <v>97</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-12.11377</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>-76.98768</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1009</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -2757,20 +3175,30 @@
           <t>TRENER DE MONTERRICO</t>
         </is>
       </c>
-      <c r="G45" t="n">
-        <v>-12.12084</v>
-      </c>
-      <c r="H45" t="n">
-        <v>-76.97656000000001</v>
-      </c>
-      <c r="I45" t="n">
-        <v>971</v>
-      </c>
-      <c r="J45" t="n">
-        <v>135</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-12.12084</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>-76.97656</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>971</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -2809,20 +3237,30 @@
           <t>VIRGEN DE LA ASUNCION</t>
         </is>
       </c>
-      <c r="G46" t="n">
-        <v>-12.14081</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-76.98298</v>
-      </c>
-      <c r="I46" t="n">
-        <v>240</v>
-      </c>
-      <c r="J46" t="n">
-        <v>26</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-12.14081</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>-76.98298</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -2861,20 +3299,30 @@
           <t>SANTA TERESITA DEL NIÑO JESUS</t>
         </is>
       </c>
-      <c r="G47" t="n">
-        <v>-12.1506</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-77.01572</v>
-      </c>
-      <c r="I47" t="n">
-        <v>227</v>
-      </c>
-      <c r="J47" t="n">
-        <v>29</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-12.1506</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>-77.01572</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -2913,20 +3361,30 @@
           <t>NUESTRA SEÑORA DEL CONSUELO</t>
         </is>
       </c>
-      <c r="G48" t="n">
-        <v>-12.11033</v>
-      </c>
-      <c r="H48" t="n">
-        <v>-76.97117</v>
-      </c>
-      <c r="I48" t="n">
-        <v>1368</v>
-      </c>
-      <c r="J48" t="n">
-        <v>110</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-12.11033</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>-76.97117</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1368</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -2965,20 +3423,30 @@
           <t>SALCANTAY</t>
         </is>
       </c>
-      <c r="G49" t="n">
-        <v>-12.09583</v>
-      </c>
-      <c r="H49" t="n">
-        <v>-76.96558</v>
-      </c>
-      <c r="I49" t="n">
-        <v>525</v>
-      </c>
-      <c r="J49" t="n">
-        <v>69</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-12.09583</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>-76.96558</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>525</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -3017,20 +3485,30 @@
           <t>CASUARINAS INTERNATIONAL COLLEGE</t>
         </is>
       </c>
-      <c r="G50" t="n">
-        <v>-12.12112</v>
-      </c>
-      <c r="H50" t="n">
-        <v>-76.97453</v>
-      </c>
-      <c r="I50" t="n">
-        <v>662</v>
-      </c>
-      <c r="J50" t="n">
-        <v>68</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-12.12112</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>-76.97453</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>662</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -3069,20 +3547,30 @@
           <t>MONTERRICO CHRISTIAN SCHOOL</t>
         </is>
       </c>
-      <c r="G51" t="n">
-        <v>-12.12431</v>
-      </c>
-      <c r="H51" t="n">
-        <v>-76.97359</v>
-      </c>
-      <c r="I51" t="n">
-        <v>237</v>
-      </c>
-      <c r="J51" t="n">
-        <v>28</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-12.12431</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>-76.97359</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -3121,20 +3609,30 @@
           <t>INTERNACIONAL DE LIMA</t>
         </is>
       </c>
-      <c r="G52" t="n">
-        <v>-12.1197</v>
-      </c>
-      <c r="H52" t="n">
-        <v>-76.99517</v>
-      </c>
-      <c r="I52" t="n">
-        <v>153</v>
-      </c>
-      <c r="J52" t="n">
-        <v>28</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0</v>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-12.1197</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>-76.99517</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -3173,20 +3671,30 @@
           <t>RAINBOW BRIGHT</t>
         </is>
       </c>
-      <c r="G53" t="n">
-        <v>-12.14364</v>
-      </c>
-      <c r="H53" t="n">
-        <v>-76.99068</v>
-      </c>
-      <c r="I53" t="n">
-        <v>13</v>
-      </c>
-      <c r="J53" t="n">
-        <v>3</v>
-      </c>
-      <c r="K53" t="n">
-        <v>1</v>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>-12.14364</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>-76.99068</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -3225,20 +3733,30 @@
           <t>SALCANTAY</t>
         </is>
       </c>
-      <c r="G54" t="n">
-        <v>-12.09796</v>
-      </c>
-      <c r="H54" t="n">
-        <v>-76.96514999999999</v>
-      </c>
-      <c r="I54" t="n">
-        <v>220</v>
-      </c>
-      <c r="J54" t="n">
-        <v>18</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0</v>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-12.09796</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>-76.96515</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -3277,20 +3795,30 @@
           <t>TRILCE MARSANO</t>
         </is>
       </c>
-      <c r="G55" t="n">
-        <v>-12.14761</v>
-      </c>
-      <c r="H55" t="n">
-        <v>-76.98304</v>
-      </c>
-      <c r="I55" t="n">
-        <v>1058</v>
-      </c>
-      <c r="J55" t="n">
-        <v>33</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>-12.14761</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>-76.98304</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1058</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -3329,20 +3857,30 @@
           <t>ESPECIAL SURCO</t>
         </is>
       </c>
-      <c r="G56" t="n">
-        <v>-12.13823</v>
-      </c>
-      <c r="H56" t="n">
-        <v>-76.98961</v>
-      </c>
-      <c r="I56" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0</v>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>-12.13823</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>-76.98961</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/LIMA-LIMA-SANTIAGO_DE_SURCO.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-SANTIAGO_DE_SURCO.xlsx
@@ -501,37 +501,37 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>317589</t>
+          <t>340759</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SANTA RITA DE CASIA</t>
+          <t>FIGURITAS</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-12.12902</t>
+          <t>-12.12812</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-77.00854</t>
+          <t>-76.99596</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>340108</t>
+          <t>340311</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>536 AMIGUITOS DE JESUS</t>
+          <t>ESPECIAL SURCO</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-12.13696</t>
+          <t>-12.13823</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-77.00099</t>
+          <t>-76.98961</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>340127</t>
+          <t>341198</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>555 INMACULADA CONCEPCION</t>
+          <t>MARKHAM</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-12.15571</t>
+          <t>-12.100516</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-76.98864</t>
+          <t>-76.976445</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>1248</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>103</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,27 +687,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>340132</t>
+          <t>340108</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>557 WARMA KUYAY</t>
+          <t>536 AMIGUITOS DE JESUS</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-12.14509</t>
+          <t>-12.13696</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-76.98359</t>
+          <t>-77.00099</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>231</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>340165</t>
+          <t>340132</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>6044 JORGE CHAVEZ</t>
+          <t>557 WARMA KUYAY</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-12.14332</t>
+          <t>-12.14509</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-77.00457</t>
+          <t>-76.98359</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1166</t>
+          <t>211</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>340170</t>
+          <t>342485</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>6047 JOSE MARIA ARGUEDAS</t>
+          <t>NUESTRA SEÑORA DEL CONSUELO</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-12.14896</t>
+          <t>-12.11033</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-76.98972</t>
+          <t>-76.97117</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1144</t>
+          <t>1368</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>110</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>340189</t>
+          <t>340212</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>6082 LOS PROCERES</t>
+          <t>7068 ABRAHAM ROLDAN POMA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-12.15068</t>
+          <t>-12.14689</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-76.98486</t>
+          <t>-77.0078</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1787</t>
+          <t>288</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>340194</t>
+          <t>340580</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>6087 PABLO MARIA GUZMAN</t>
+          <t>CORAZON INMACULADO</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-12.09525</t>
+          <t>-12.14443</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-76.96393</t>
+          <t>-76.98693</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>96</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>340207</t>
+          <t>341933</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>7058 MARIA DE FATIMA</t>
+          <t>TRENER DE MONTERRICO</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-12.14506</t>
+          <t>-12.12084</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-77.00426</t>
+          <t>-76.97656</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>971</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>135</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>340212</t>
+          <t>340127</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>7068 ABRAHAM ROLDAN POMA</t>
+          <t>555 INMACULADA CONCEPCION</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-12.14689</t>
+          <t>-12.15571</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-77.0078</t>
+          <t>-76.98864</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>299</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>340226</t>
+          <t>340245</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>7068 ABRAHAM ROLDAN POMA</t>
+          <t>086 VIRGENCITA DEL CARMEN</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-12.14561</t>
+          <t>-12.14468</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-77.0061</t>
+          <t>-77.00405</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>286</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>340231</t>
+          <t>340962</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>7086 LOS PRECURSORES</t>
+          <t>COLEGIO DE LA INMACULADA (JESUITAS)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-12.15677</t>
+          <t>-12.13024</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-76.9858</t>
+          <t>-76.97277</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1888</t>
+          <t>1515</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>151</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>340245</t>
+          <t>340306</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>086 VIRGENCITA DEL CARMEN</t>
+          <t>VICTORIA BARCIA BONIFFATTI</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-12.14468</t>
+          <t>-12.12039</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-77.00405</t>
+          <t>-76.9934</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>305</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>340250</t>
+          <t>341184</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>87 CORAZON DE MARIA</t>
+          <t>MARISCAL CACERES</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-12.15392</t>
+          <t>-12.14641</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-76.98664</t>
+          <t>-77.00793</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>206</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,27 +1369,27 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>340306</t>
+          <t>341565</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>VICTORIA BARCIA BONIFFATTI</t>
+          <t>RICHARD BACH</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-12.12039</t>
+          <t>-12.15706</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-76.9934</t>
+          <t>-76.98747</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>242</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>340325</t>
+          <t>340250</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>7087 SANTIAGO DE SURCO</t>
+          <t>87 CORAZON DE MARIA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-12.143777</t>
+          <t>-12.15392</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-76.983364</t>
+          <t>-76.98664</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>436</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>340330</t>
+          <t>340698</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>PNP CAP. ALCIDES VIGO HURTADO</t>
+          <t>VILLA ALEGRE</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-12.12264</t>
+          <t>-12.16562</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-76.99421</t>
+          <t>-76.99159</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>227</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>340387</t>
+          <t>743020</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ANDRE MALRAUX</t>
+          <t>SALCANTAY</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-12.12482</t>
+          <t>-12.09796</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-76.97922</t>
+          <t>-76.96515</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>220</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,37 +1617,37 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>340580</t>
+          <t>340801</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CORAZON INMACULADO</t>
+          <t>GOTITAS DE CRISTAL</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-12.14443</t>
+          <t>-12.14778</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-76.98693</t>
+          <t>-77.00955</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>340622</t>
+          <t>340325</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>CRISTO SALVADOR</t>
+          <t>7087 SANTIAGO DE SURCO</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-12.12681</t>
+          <t>-12.143777</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-76.99563</t>
+          <t>-76.983364</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>752</t>
+          <t>470</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>340698</t>
+          <t>341711</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>VILLA ALEGRE</t>
+          <t>SAN MARCOS DE MONTERRICO</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-12.16562</t>
+          <t>-12.1277</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-76.99159</t>
+          <t>-76.97418</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>128</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1803,42 +1803,42 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>340759</t>
+          <t>341730</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>FIGURITAS</t>
+          <t>SAN ROQUE</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-12.12812</t>
+          <t>-12.14834</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-76.99596</t>
+          <t>-76.98878</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>329</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1865,37 +1865,37 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>340801</t>
+          <t>341382</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>GOTITAS DE CRISTAL</t>
+          <t>NUEVO MUNDO</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-12.14778</t>
+          <t>-12.12289</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-77.00955</t>
+          <t>-76.99456</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>388</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>340844</t>
+          <t>341631</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>HORACIO PATIÑO CRUZATTI</t>
+          <t>SAN BENITO DE PALERMO</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-12.13197</t>
+          <t>-12.15057</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-76.98582</t>
+          <t>-76.98875</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>364</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,37 +1989,37 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>340938</t>
+          <t>341985</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>JUAN JACOBO ROUSSEAU</t>
+          <t>VIRGEN DE LA ASUNCION</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-12.08386</t>
+          <t>-12.14081</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-76.97856</t>
+          <t>-76.98298</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>240</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>340962</t>
+          <t>341344</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>COLEGIO DE LA INMACULADA (JESUITAS)</t>
+          <t>NUESTRA SEÑORA DE LA ASUNCION</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-12.13024</t>
+          <t>-12.14435</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-76.97277</t>
+          <t>-76.98687</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1515</t>
+          <t>196</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>340976</t>
+          <t>340226</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>LA INMACULADA CONCEPCION</t>
+          <t>7068 ABRAHAM ROLDAN POMA</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-12.12794</t>
+          <t>-12.14561</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-76.99928</t>
+          <t>-77.0061</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1494</t>
+          <t>592</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>341103</t>
+          <t>724352</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>MAGISTER</t>
+          <t>MONTERRICO CHRISTIAN SCHOOL</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-12.10407</t>
+          <t>-12.12431</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-76.97758</t>
+          <t>-76.97359</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>237</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>341184</t>
+          <t>725158</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>MARISCAL CACERES</t>
+          <t>INTERNACIONAL DE LIMA</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-12.14641</t>
+          <t>-12.1197</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-77.00793</t>
+          <t>-76.99517</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>153</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>341198</t>
+          <t>342329</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>MARKHAM</t>
+          <t>SANTA TERESITA DEL NIÑO JESUS</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-12.100516</t>
+          <t>-12.1506</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-76.976445</t>
+          <t>-77.01572</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1248</t>
+          <t>227</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,37 +2361,37 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>341216</t>
+          <t>725484</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>MATER CHRISTI</t>
+          <t>RAINBOW BRIGHT</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-12.12488</t>
+          <t>-12.14364</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-76.98245</t>
+          <t>-76.99068</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>341344</t>
+          <t>341749</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE LA ASUNCION</t>
+          <t>SANTA ISABEL</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-12.14435</t>
+          <t>-12.13333</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-76.98687</t>
+          <t>-76.99427</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>212</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>341382</t>
+          <t>340207</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>NUEVO MUNDO</t>
+          <t>7058 MARIA DE FATIMA</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-12.12289</t>
+          <t>-12.14506</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-76.99456</t>
+          <t>-77.00426</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>620</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>341476</t>
+          <t>858836</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>PERUANO BRITANICO</t>
+          <t>TRILCE MARSANO</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-12.09255</t>
+          <t>-12.14761</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-76.97345</t>
+          <t>-76.98304</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>1058</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>341508</t>
+          <t>340194</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>PIO XII</t>
+          <t>6087 PABLO MARIA GUZMAN</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-12.0979</t>
+          <t>-12.09525</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-76.96535</t>
+          <t>-76.96393</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>575</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>341565</t>
+          <t>340387</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>RICHARD BACH</t>
+          <t>ANDRE MALRAUX</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-12.15706</t>
+          <t>-12.12482</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-76.98747</t>
+          <t>-76.97922</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>372</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>341631</t>
+          <t>340330</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>SAN BENITO DE PALERMO</t>
+          <t>PNP CAP. ALCIDES VIGO HURTADO</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-12.15057</t>
+          <t>-12.12264</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-76.98875</t>
+          <t>-76.99421</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>629</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>341674</t>
+          <t>341216</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>SAN JOSE DE MONTERRICO</t>
+          <t>MATER CHRISTI</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-12.10991</t>
+          <t>-12.12488</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-76.96776</t>
+          <t>-76.98245</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>994</t>
+          <t>456</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>43</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>341711</t>
+          <t>340844</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>SAN MARCOS DE MONTERRICO</t>
+          <t>HORACIO PATIÑO CRUZATTI</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-12.1277</t>
+          <t>-12.13197</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-76.97418</t>
+          <t>-76.98582</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>622</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>46</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>341730</t>
+          <t>341103</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>SAN ROQUE</t>
+          <t>MAGISTER</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-12.14834</t>
+          <t>-12.10407</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-76.98878</t>
+          <t>-76.97758</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>509</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>51</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>341749</t>
+          <t>317589</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>SANTA ISABEL</t>
+          <t>SANTA RITA DE CASIA</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-12.13333</t>
+          <t>-12.12902</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-76.99427</t>
+          <t>-77.00854</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>593</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>52</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>341773</t>
+          <t>341508</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>SANTA MARGARITA</t>
+          <t>PIO XII</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-12.10094</t>
+          <t>-12.0979</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-76.973</t>
+          <t>-76.96535</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>718</t>
+          <t>356</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>57</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>341787</t>
+          <t>340170</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>SANTA MARIA MARIANISTA</t>
+          <t>6047 JOSE MARIA ARGUEDAS</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-12.11377</t>
+          <t>-12.14896</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-76.98768</t>
+          <t>-76.98972</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>1144</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>341933</t>
+          <t>340165</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>TRENER DE MONTERRICO</t>
+          <t>6044 JORGE CHAVEZ</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-12.12084</t>
+          <t>-12.14332</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-76.97656</t>
+          <t>-77.00457</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>1166</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>61</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>341985</t>
+          <t>341773</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>VIRGEN DE LA ASUNCION</t>
+          <t>SANTA MARGARITA</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-12.14081</t>
+          <t>-12.10094</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-76.98298</t>
+          <t>-76.973</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>718</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>62</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3291,32 +3291,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>342329</t>
+          <t>723852</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>SANTA TERESITA DEL NIÑO JESUS</t>
+          <t>CASUARINAS INTERNATIONAL COLLEGE</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-12.1506</t>
+          <t>-12.12112</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-77.01572</t>
+          <t>-76.97453</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>662</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>68</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>342485</t>
+          <t>342744</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DEL CONSUELO</t>
+          <t>SALCANTAY</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-12.11033</t>
+          <t>-12.09583</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-76.97117</t>
+          <t>-76.96558</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1368</t>
+          <t>525</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>69</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>342744</t>
+          <t>340622</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>SALCANTAY</t>
+          <t>CRISTO SALVADOR</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-12.09583</t>
+          <t>-12.12681</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-76.96558</t>
+          <t>-76.99563</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>525</t>
+          <t>752</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>74</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3477,32 +3477,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>723852</t>
+          <t>341476</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>CASUARINAS INTERNATIONAL COLLEGE</t>
+          <t>PERUANO BRITANICO</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-12.12112</t>
+          <t>-12.09255</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-76.97453</t>
+          <t>-76.97345</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>964</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>80</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>724352</t>
+          <t>340976</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>MONTERRICO CHRISTIAN SCHOOL</t>
+          <t>LA INMACULADA CONCEPCION</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-12.12431</t>
+          <t>-12.12794</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-76.97359</t>
+          <t>-76.99928</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>1494</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>85</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3601,42 +3601,42 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>725158</t>
+          <t>340938</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>INTERNACIONAL DE LIMA</t>
+          <t>JUAN JACOBO ROUSSEAU</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-12.1197</t>
+          <t>-12.08386</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-76.99517</t>
+          <t>-76.97856</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3663,37 +3663,37 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>725484</t>
+          <t>340231</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>RAINBOW BRIGHT</t>
+          <t>7086 LOS PRECURSORES</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-12.14364</t>
+          <t>-12.15677</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-76.99068</t>
+          <t>-76.9858</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1888</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>90</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3725,32 +3725,32 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>743020</t>
+          <t>340189</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>SALCANTAY</t>
+          <t>6082 LOS PROCERES</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-12.09796</t>
+          <t>-12.15068</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-76.96515</t>
+          <t>-76.98486</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>1787</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>92</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3787,32 +3787,32 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>858836</t>
+          <t>341674</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>TRILCE MARSANO</t>
+          <t>SAN JOSE DE MONTERRICO</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-12.14761</t>
+          <t>-12.10991</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>-76.98304</t>
+          <t>-76.96776</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1058</t>
+          <t>994</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>94</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3849,32 +3849,32 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>340311</t>
+          <t>341787</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>ESPECIAL SURCO</t>
+          <t>SANTA MARIA MARIANISTA</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-12.13823</t>
+          <t>-12.11377</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>-76.98961</t>
+          <t>-76.98768</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1009</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>97</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/LIMA-LIMA-SANTIAGO_DE_SURCO.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-SANTIAGO_DE_SURCO.xlsx
@@ -501,37 +501,37 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>340759</t>
+          <t>858836</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>FIGURITAS</t>
+          <t>TRILCE MARSANO</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-12.12812</t>
+          <t>1058</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-76.99596</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-12.14761</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-76.98304</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>340311</t>
+          <t>743020</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ESPECIAL SURCO</t>
+          <t>SALCANTAY</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-12.13823</t>
+          <t>220</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-76.98961</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-12.09796</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-76.96515</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -598,7 +598,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -625,37 +625,37 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>341198</t>
+          <t>725484</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MARKHAM</t>
+          <t>RAINBOW BRIGHT</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-12.100516</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-76.976445</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1248</t>
+          <t>-12.14364</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>-76.99068</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>340108</t>
+          <t>725158</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>536 AMIGUITOS DE JESUS</t>
+          <t>INTERNACIONAL DE LIMA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-12.13696</t>
+          <t>153</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-77.00099</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>-12.1197</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-76.99517</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>340132</t>
+          <t>724352</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>557 WARMA KUYAY</t>
+          <t>MONTERRICO CHRISTIAN SCHOOL</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-12.14509</t>
+          <t>237</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-76.98359</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>-12.12431</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-76.97359</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>342485</t>
+          <t>723852</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DEL CONSUELO</t>
+          <t>CASUARINAS INTERNATIONAL COLLEGE</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-12.11033</t>
+          <t>662</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-76.97117</t>
+          <t>68</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1368</t>
+          <t>-12.12112</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>-76.97453</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>340212</t>
+          <t>342744</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>7068 ABRAHAM ROLDAN POMA</t>
+          <t>SALCANTAY</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-12.14689</t>
+          <t>525</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-77.0078</t>
+          <t>69</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>-12.09583</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-76.96558</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>340580</t>
+          <t>342485</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CORAZON INMACULADO</t>
+          <t>NUESTRA SEÑORA DEL CONSUELO</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-12.14443</t>
+          <t>1368</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-76.98693</t>
+          <t>110</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>-12.11033</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-76.97117</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>341933</t>
+          <t>342329</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>TRENER DE MONTERRICO</t>
+          <t>SANTA TERESITA DEL NIÑO JESUS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-12.12084</t>
+          <t>227</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-76.97656</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>-12.1506</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>-77.01572</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>340127</t>
+          <t>341985</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>555 INMACULADA CONCEPCION</t>
+          <t>VIRGEN DE LA ASUNCION</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-12.15571</t>
+          <t>240</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-76.98864</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>-12.14081</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-76.98298</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>340245</t>
+          <t>341933</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>086 VIRGENCITA DEL CARMEN</t>
+          <t>TRENER DE MONTERRICO</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-12.14468</t>
+          <t>971</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-77.00405</t>
+          <t>135</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>-12.12084</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-76.97656</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>340962</t>
+          <t>341787</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>COLEGIO DE LA INMACULADA (JESUITAS)</t>
+          <t>SANTA MARIA MARIANISTA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-12.13024</t>
+          <t>1009</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-76.97277</t>
+          <t>97</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1515</t>
+          <t>-12.11377</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>-76.98768</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>340306</t>
+          <t>341773</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>VICTORIA BARCIA BONIFFATTI</t>
+          <t>SANTA MARGARITA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-12.12039</t>
+          <t>718</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-76.9934</t>
+          <t>62</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>-12.10094</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-76.973</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>341184</t>
+          <t>341749</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MARISCAL CACERES</t>
+          <t>SANTA ISABEL</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-12.14641</t>
+          <t>212</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-77.00793</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>-12.13333</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-76.99427</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>341565</t>
+          <t>341730</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>RICHARD BACH</t>
+          <t>SAN ROQUE</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-12.15706</t>
+          <t>329</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-76.98747</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>-12.14834</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-76.98878</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>340250</t>
+          <t>341711</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>87 CORAZON DE MARIA</t>
+          <t>SAN MARCOS DE MONTERRICO</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-12.15392</t>
+          <t>128</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-76.98664</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>-12.1277</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-76.97418</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>340698</t>
+          <t>341674</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>VILLA ALEGRE</t>
+          <t>SAN JOSE DE MONTERRICO</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-12.16562</t>
+          <t>994</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-76.99159</t>
+          <t>94</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>-12.10991</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-76.96776</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>743020</t>
+          <t>341631</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SALCANTAY</t>
+          <t>SAN BENITO DE PALERMO</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-12.09796</t>
+          <t>364</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-76.96515</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>-12.15057</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-76.98875</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,37 +1617,37 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>340801</t>
+          <t>341565</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>GOTITAS DE CRISTAL</t>
+          <t>RICHARD BACH</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-12.14778</t>
+          <t>242</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-77.00955</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-12.15706</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-76.98747</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>340325</t>
+          <t>341508</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>7087 SANTIAGO DE SURCO</t>
+          <t>PIO XII</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-12.143777</t>
+          <t>356</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-76.983364</t>
+          <t>57</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>-12.0979</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-76.96535</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>341711</t>
+          <t>341476</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SAN MARCOS DE MONTERRICO</t>
+          <t>PERUANO BRITANICO</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-12.1277</t>
+          <t>964</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-76.97418</t>
+          <t>80</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>-12.09255</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-76.97345</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>341730</t>
+          <t>341382</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SAN ROQUE</t>
+          <t>NUEVO MUNDO</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-12.14834</t>
+          <t>388</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-76.98878</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>-12.12289</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-76.99456</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>341382</t>
+          <t>341344</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>NUEVO MUNDO</t>
+          <t>NUESTRA SEÑORA DE LA ASUNCION</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-12.12289</t>
+          <t>196</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-76.99456</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>-12.14435</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-76.98687</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>341631</t>
+          <t>341216</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>SAN BENITO DE PALERMO</t>
+          <t>MATER CHRISTI</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-12.15057</t>
+          <t>456</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-76.98875</t>
+          <t>43</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>-12.12488</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-76.98245</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>341985</t>
+          <t>341198</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>VIRGEN DE LA ASUNCION</t>
+          <t>MARKHAM</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-12.14081</t>
+          <t>1248</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-76.98298</t>
+          <t>103</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>-12.100516</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-76.976445</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>341344</t>
+          <t>341184</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE LA ASUNCION</t>
+          <t>MARISCAL CACERES</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-12.14435</t>
+          <t>206</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-76.98687</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>-12.14641</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-77.00793</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>340226</t>
+          <t>341103</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>7068 ABRAHAM ROLDAN POMA</t>
+          <t>MAGISTER</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-12.14561</t>
+          <t>509</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-77.0061</t>
+          <t>51</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>-12.10407</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-76.97758</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>724352</t>
+          <t>340976</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>MONTERRICO CHRISTIAN SCHOOL</t>
+          <t>LA INMACULADA CONCEPCION</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-12.12431</t>
+          <t>1494</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-76.97359</t>
+          <t>85</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>-12.12794</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-76.99928</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>725158</t>
+          <t>340962</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>INTERNACIONAL DE LIMA</t>
+          <t>COLEGIO DE LA INMACULADA (JESUITAS)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-12.1197</t>
+          <t>1515</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-76.99517</t>
+          <t>151</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>-12.13024</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-76.97277</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2299,37 +2299,37 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>342329</t>
+          <t>340938</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>SANTA TERESITA DEL NIÑO JESUS</t>
+          <t>JUAN JACOBO ROUSSEAU</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-12.1506</t>
+          <t>17</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-77.01572</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>-12.08386</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-76.97856</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2361,37 +2361,37 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>725484</t>
+          <t>340844</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>RAINBOW BRIGHT</t>
+          <t>HORACIO PATIÑO CRUZATTI</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-12.14364</t>
+          <t>622</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-76.99068</t>
+          <t>46</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-12.13197</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-76.98582</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2423,42 +2423,42 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>341749</t>
+          <t>340801</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>SANTA ISABEL</t>
+          <t>GOTITAS DE CRISTAL</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-12.13333</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-76.99427</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>-12.14778</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-77.00955</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2485,37 +2485,37 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>340207</t>
+          <t>340759</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>7058 MARIA DE FATIMA</t>
+          <t>FIGURITAS</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-12.14506</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-77.00426</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>-12.12812</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-76.99596</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>858836</t>
+          <t>340698</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>TRILCE MARSANO</t>
+          <t>VILLA ALEGRE</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-12.14761</t>
+          <t>227</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-76.98304</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1058</t>
+          <t>-12.16562</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>-76.99159</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>340194</t>
+          <t>340622</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>6087 PABLO MARIA GUZMAN</t>
+          <t>CRISTO SALVADOR</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-12.09525</t>
+          <t>752</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-76.96393</t>
+          <t>74</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>-12.12681</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-76.99563</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>340387</t>
+          <t>340580</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>ANDRE MALRAUX</t>
+          <t>CORAZON INMACULADO</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-12.12482</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-76.97922</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>-12.14443</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>-76.98693</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>340330</t>
+          <t>340387</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>PNP CAP. ALCIDES VIGO HURTADO</t>
+          <t>ANDRE MALRAUX</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-12.12264</t>
+          <t>372</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-76.99421</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>-12.12482</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>-76.97922</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>341216</t>
+          <t>340330</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>MATER CHRISTI</t>
+          <t>PNP CAP. ALCIDES VIGO HURTADO</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-12.12488</t>
+          <t>629</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-76.98245</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>-12.12264</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>-76.99421</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>340844</t>
+          <t>340325</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>HORACIO PATIÑO CRUZATTI</t>
+          <t>7087 SANTIAGO DE SURCO</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-12.13197</t>
+          <t>470</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-76.98582</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>-12.143777</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>-76.983364</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>341103</t>
+          <t>340311</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>MAGISTER</t>
+          <t>ESPECIAL SURCO</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-12.10407</t>
+          <t>116</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-76.97758</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>-12.13823</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>-76.98961</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>317589</t>
+          <t>340306</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>SANTA RITA DE CASIA</t>
+          <t>VICTORIA BARCIA BONIFFATTI</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-12.12902</t>
+          <t>305</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-77.00854</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>-12.12039</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>-76.9934</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>341508</t>
+          <t>340250</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>PIO XII</t>
+          <t>87 CORAZON DE MARIA</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-12.0979</t>
+          <t>436</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-76.96535</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>-12.15392</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>-76.98664</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>340170</t>
+          <t>340245</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>6047 JOSE MARIA ARGUEDAS</t>
+          <t>086 VIRGENCITA DEL CARMEN</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-12.14896</t>
+          <t>286</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-76.98972</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1144</t>
+          <t>-12.14468</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>-77.00405</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>340165</t>
+          <t>340231</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>6044 JORGE CHAVEZ</t>
+          <t>7086 LOS PRECURSORES</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-12.14332</t>
+          <t>1888</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-77.00457</t>
+          <t>90</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1166</t>
+          <t>-12.15677</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>-76.9858</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>341773</t>
+          <t>340226</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>SANTA MARGARITA</t>
+          <t>7068 ABRAHAM ROLDAN POMA</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-12.10094</t>
+          <t>592</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-76.973</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>718</t>
+          <t>-12.14561</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>-77.0061</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3291,32 +3291,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>723852</t>
+          <t>340212</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>CASUARINAS INTERNATIONAL COLLEGE</t>
+          <t>7068 ABRAHAM ROLDAN POMA</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-12.12112</t>
+          <t>288</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-76.97453</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>-12.14689</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>-77.0078</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>342744</t>
+          <t>340207</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>SALCANTAY</t>
+          <t>7058 MARIA DE FATIMA</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-12.09583</t>
+          <t>620</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-76.96558</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>525</t>
+          <t>-12.14506</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>-77.00426</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>340622</t>
+          <t>340194</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>CRISTO SALVADOR</t>
+          <t>6087 PABLO MARIA GUZMAN</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-12.12681</t>
+          <t>575</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-76.99563</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>752</t>
+          <t>-12.09525</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>-76.96393</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3477,32 +3477,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>341476</t>
+          <t>340189</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>PERUANO BRITANICO</t>
+          <t>6082 LOS PROCERES</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-12.09255</t>
+          <t>1787</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-76.97345</t>
+          <t>92</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>-12.15068</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>-76.98486</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>340976</t>
+          <t>340170</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>LA INMACULADA CONCEPCION</t>
+          <t>6047 JOSE MARIA ARGUEDAS</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-12.12794</t>
+          <t>1144</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-76.99928</t>
+          <t>59</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1494</t>
+          <t>-12.14896</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>-76.98972</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3601,37 +3601,37 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>340938</t>
+          <t>340165</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>JUAN JACOBO ROUSSEAU</t>
+          <t>6044 JORGE CHAVEZ</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-12.08386</t>
+          <t>1166</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-76.97856</t>
+          <t>61</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-12.14332</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-77.00457</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3663,32 +3663,32 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>340231</t>
+          <t>340132</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>7086 LOS PRECURSORES</t>
+          <t>557 WARMA KUYAY</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-12.15677</t>
+          <t>211</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-76.9858</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1888</t>
+          <t>-12.14509</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>-76.98359</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3725,32 +3725,32 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>340189</t>
+          <t>340127</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>6082 LOS PROCERES</t>
+          <t>555 INMACULADA CONCEPCION</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-12.15068</t>
+          <t>299</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-76.98486</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1787</t>
+          <t>-12.15571</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>-76.98864</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3787,32 +3787,32 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>341674</t>
+          <t>340108</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>SAN JOSE DE MONTERRICO</t>
+          <t>536 AMIGUITOS DE JESUS</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-12.10991</t>
+          <t>231</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>-76.96776</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>994</t>
+          <t>-12.13696</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>-77.00099</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3849,32 +3849,32 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>341787</t>
+          <t>317589</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>SANTA MARIA MARIANISTA</t>
+          <t>SANTA RITA DE CASIA</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-12.11377</t>
+          <t>593</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>-76.98768</t>
+          <t>52</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>-12.12902</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>-77.00854</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">

--- a/ZonasEscolares/excels/LIMA-LIMA-SANTIAGO_DE_SURCO.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-SANTIAGO_DE_SURCO.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
